--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,10 +70,6 @@
   </si>
   <si>
     <t>回收资金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -453,7 +449,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -621,6 +617,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -630,7 +629,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -797,6 +796,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -840,7 +842,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1008,6 +1010,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1017,7 +1022,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1185,6 +1190,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>13579330.276349539</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>14184787.163745383</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,7 +1235,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1395,6 +1403,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1404,7 +1415,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1572,6 +1583,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4202938.088629419</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4808394.9760252628</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1593,11 +1607,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="557966080"/>
-        <c:axId val="557967616"/>
+        <c:axId val="528468224"/>
+        <c:axId val="528478208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="557966080"/>
+        <c:axId val="528468224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1640,14 +1654,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557967616"/>
+        <c:crossAx val="528478208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="557967616"/>
+        <c:axId val="528478208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1698,7 +1712,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="557966080"/>
+        <c:crossAx val="528468224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1889,7 +1903,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2057,6 +2071,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-63583.378859762786</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-109430.44453916258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,8 +2088,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="566731520"/>
-        <c:axId val="560663552"/>
+        <c:axId val="684677760"/>
+        <c:axId val="680907136"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2097,7 +2114,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2265,6 +2282,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2274,7 +2294,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2442,6 +2462,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4.8240952148437497</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.0477412109374997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,11 +2481,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="558140800"/>
-        <c:axId val="558163072"/>
+        <c:axId val="528598144"/>
+        <c:axId val="528600448"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="558140800"/>
+        <c:axId val="528598144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2505,14 +2528,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558163072"/>
+        <c:crossAx val="528600448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="558163072"/>
+        <c:axId val="528600448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2563,12 +2586,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="558140800"/>
+        <c:crossAx val="528598144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="560663552"/>
+        <c:axId val="680907136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2605,12 +2628,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="566731520"/>
+        <c:crossAx val="684677760"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="566731520"/>
+        <c:axId val="684677760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2642,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="560663552"/>
+        <c:crossAx val="680907136"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3028,7 +3051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3105,7 +3128,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3157,13 +3180,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>13</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3175,10 +3198,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="26" t="s">
         <v>15</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5502,6 +5525,44 @@
       </c>
       <c r="L58" s="16">
         <v>519486.93331861048</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="14">
+        <v>46022</v>
+      </c>
+      <c r="B59" s="15">
+        <v>5.0477412109374997</v>
+      </c>
+      <c r="C59" s="15">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D59" s="16">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E59" s="16">
+        <v>-109430.44453916258</v>
+      </c>
+      <c r="F59" s="17">
+        <v>-21679.09168997165</v>
+      </c>
+      <c r="G59" s="17">
+        <v>2685531.8486840422</v>
+      </c>
+      <c r="H59" s="17">
+        <v>13555869.78588761</v>
+      </c>
+      <c r="I59" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J59" s="17">
+        <v>14184787.163745383</v>
+      </c>
+      <c r="K59" s="17">
+        <v>4808394.9760252628</v>
+      </c>
+      <c r="L59" s="16">
+        <v>628917.3778577731</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,6 +70,10 @@
   </si>
   <si>
     <t>回收资金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -449,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -620,6 +624,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -629,7 +636,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -799,6 +806,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -842,7 +852,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1013,6 +1023,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1022,7 +1035,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1193,6 +1206,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>14184787.163745383</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14524323.361325197</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1235,7 +1251,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1406,6 +1422,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1415,7 +1434,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1586,6 +1605,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>4808394.9760252628</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5147931.173605077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1607,11 +1629,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528468224"/>
-        <c:axId val="528478208"/>
+        <c:axId val="616540800"/>
+        <c:axId val="617828736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528468224"/>
+        <c:axId val="616540800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1654,14 +1676,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528478208"/>
+        <c:crossAx val="617828736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528478208"/>
+        <c:axId val="617828736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1712,7 +1734,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528468224"/>
+        <c:crossAx val="616540800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1903,7 +1925,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2074,6 +2096,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-109430.44453916258</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-129990.80506332006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2088,8 +2113,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="684677760"/>
-        <c:axId val="680907136"/>
+        <c:axId val="621649280"/>
+        <c:axId val="621647360"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2114,7 +2139,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2285,6 +2310,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2294,7 +2322,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2465,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5.0477412109374997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.1741728515625001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,11 +2512,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="528598144"/>
-        <c:axId val="528600448"/>
+        <c:axId val="617949824"/>
+        <c:axId val="621645824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="528598144"/>
+        <c:axId val="617949824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2528,14 +2559,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528600448"/>
+        <c:crossAx val="621645824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528600448"/>
+        <c:axId val="621645824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,12 +2617,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528598144"/>
+        <c:crossAx val="617949824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="680907136"/>
+        <c:axId val="621647360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2628,12 +2659,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="684677760"/>
+        <c:crossAx val="621649280"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="684677760"/>
+        <c:axId val="621649280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2642,7 +2673,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="680907136"/>
+        <c:crossAx val="621647360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3051,7 +3082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3128,7 +3159,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3180,13 +3211,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3198,10 +3229,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5563,6 +5594,44 @@
       </c>
       <c r="L59" s="16">
         <v>628917.3778577731</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B60" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C60" s="15">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D60" s="16">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E60" s="16">
+        <v>-129990.80506332006</v>
+      </c>
+      <c r="F60" s="17">
+        <v>-25123.011695302244</v>
+      </c>
+      <c r="G60" s="17">
+        <v>2660408.8369887401</v>
+      </c>
+      <c r="H60" s="17">
+        <v>13765415.178404104</v>
+      </c>
+      <c r="I60" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J60" s="17">
+        <v>14524323.361325197</v>
+      </c>
+      <c r="K60" s="17">
+        <v>5147931.173605077</v>
+      </c>
+      <c r="L60" s="16">
+        <v>758908.18292109319</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -627,6 +627,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -636,7 +639,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -809,6 +812,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -852,7 +858,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1026,6 +1032,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1035,7 +1044,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1209,6 +1218,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>14524323.361325197</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14380272.874829827</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1251,7 +1263,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1425,6 +1437,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,7 +1449,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1608,6 +1623,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5147931.173605077</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5003880.6871097069</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1629,11 +1647,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="616540800"/>
-        <c:axId val="617828736"/>
+        <c:axId val="474931584"/>
+        <c:axId val="474933504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="616540800"/>
+        <c:axId val="474931584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1676,14 +1694,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617828736"/>
+        <c:crossAx val="474933504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617828736"/>
+        <c:axId val="474933504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1734,7 +1752,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616540800"/>
+        <c:crossAx val="474931584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1925,7 +1943,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2099,6 +2117,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-129990.80506332006</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-119930.28329170092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2113,8 +2134,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="621649280"/>
-        <c:axId val="621647360"/>
+        <c:axId val="511991808"/>
+        <c:axId val="475035904"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2139,7 +2160,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2313,6 +2334,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2322,7 +2346,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2496,6 +2520,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5.1741728515625001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.1200268554687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2512,11 +2539,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617949824"/>
-        <c:axId val="621645824"/>
+        <c:axId val="475027328"/>
+        <c:axId val="475034368"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617949824"/>
+        <c:axId val="475027328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2559,14 +2586,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621645824"/>
+        <c:crossAx val="475034368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621645824"/>
+        <c:axId val="475034368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2617,12 +2644,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617949824"/>
+        <c:crossAx val="475027328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="621647360"/>
+        <c:axId val="475035904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2659,12 +2686,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621649280"/>
+        <c:crossAx val="511991808"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="621649280"/>
+        <c:axId val="511991808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2673,7 +2700,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="621647360"/>
+        <c:crossAx val="475035904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3082,7 +3109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5634,6 +5661,44 @@
         <v>758908.18292109319</v>
       </c>
     </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B61" s="15">
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="C61" s="15">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D61" s="16">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E61" s="16">
+        <v>-119930.28329170092</v>
+      </c>
+      <c r="F61" s="17">
+        <v>-23423.760592896546</v>
+      </c>
+      <c r="G61" s="17">
+        <v>2636985.0763958436</v>
+      </c>
+      <c r="H61" s="17">
+        <v>13501434.408617033</v>
+      </c>
+      <c r="I61" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J61" s="17">
+        <v>14380272.874829827</v>
+      </c>
+      <c r="K61" s="17">
+        <v>5003880.6871097069</v>
+      </c>
+      <c r="L61" s="16">
+        <v>878838.46621279407</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,10 +70,6 @@
   </si>
   <si>
     <t>回收资金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -453,7 +449,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -630,6 +626,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -639,7 +638,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -815,6 +814,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -858,7 +860,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1035,6 +1037,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1044,7 +1049,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1221,6 +1226,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>14380272.874829827</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>13760930.318866894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1263,7 +1271,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1440,6 +1448,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1449,7 +1460,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1626,6 +1637,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>5003880.6871097069</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4384538.1311467737</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1647,11 +1661,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="474931584"/>
-        <c:axId val="474933504"/>
+        <c:axId val="527200256"/>
+        <c:axId val="527201792"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="474931584"/>
+        <c:axId val="527200256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1694,14 +1708,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474933504"/>
+        <c:crossAx val="527201792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="474933504"/>
+        <c:axId val="527201792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1752,7 +1766,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474931584"/>
+        <c:crossAx val="527200256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1943,7 +1957,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2120,6 +2134,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-119930.28329170092</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-76925.150887958705</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2134,8 +2151,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="511991808"/>
-        <c:axId val="475035904"/>
+        <c:axId val="588359168"/>
+        <c:axId val="588351744"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2160,7 +2177,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2337,6 +2354,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,7 +2366,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2523,6 +2543,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>5.1200268554687502</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.8851591796875002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2539,11 +2562,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="475027328"/>
-        <c:axId val="475034368"/>
+        <c:axId val="538437888"/>
+        <c:axId val="588350208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="475027328"/>
+        <c:axId val="538437888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,14 +2609,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475034368"/>
+        <c:crossAx val="588350208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="475034368"/>
+        <c:axId val="588350208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,12 +2667,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="475027328"/>
+        <c:crossAx val="538437888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="475035904"/>
+        <c:axId val="588351744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2686,12 +2709,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511991808"/>
+        <c:crossAx val="588359168"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="511991808"/>
+        <c:axId val="588359168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2700,7 +2723,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="475035904"/>
+        <c:crossAx val="588351744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3109,7 +3132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3186,7 +3209,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3238,13 +3261,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>13</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3256,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="26" t="s">
         <v>15</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5697,6 +5720,44 @@
       </c>
       <c r="L61" s="16">
         <v>878838.46621279407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B62" s="15">
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="C62" s="15">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D62" s="16">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E62" s="16">
+        <v>-76925.150887958705</v>
+      </c>
+      <c r="F62" s="17">
+        <v>-15746.70303637466</v>
+      </c>
+      <c r="G62" s="17">
+        <v>2621238.3733594688</v>
+      </c>
+      <c r="H62" s="17">
+        <v>12805166.701766141</v>
+      </c>
+      <c r="I62" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J62" s="17">
+        <v>13760930.318866894</v>
+      </c>
+      <c r="K62" s="17">
+        <v>4384538.1311467737</v>
+      </c>
+      <c r="L62" s="16">
+        <v>955763.61710075277</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,6 +70,10 @@
   </si>
   <si>
     <t>回收资金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -449,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -629,6 +633,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -638,7 +645,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -817,6 +824,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -860,7 +870,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1040,6 +1050,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1049,7 +1062,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1229,6 +1242,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>13760930.318866894</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>15492648.634443415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1271,7 +1287,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1451,6 +1467,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1460,7 +1479,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1640,6 +1659,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>4384538.1311467737</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6116256.4467232954</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1661,11 +1683,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527200256"/>
-        <c:axId val="527201792"/>
+        <c:axId val="530836480"/>
+        <c:axId val="573232640"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527200256"/>
+        <c:axId val="530836480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1708,14 +1730,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527201792"/>
+        <c:crossAx val="573232640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="527201792"/>
+        <c:axId val="573232640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1766,7 +1788,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527200256"/>
+        <c:crossAx val="530836480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1957,7 +1979,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2137,6 +2159,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-76925.150887958705</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-271948.26049911132</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2151,8 +2176,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="588359168"/>
-        <c:axId val="588351744"/>
+        <c:axId val="617399040"/>
+        <c:axId val="617384576"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2177,7 +2202,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2357,6 +2382,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2366,7 +2394,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2546,6 +2574,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>4.8851591796875002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.5458081054687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,11 +2593,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="538437888"/>
-        <c:axId val="588350208"/>
+        <c:axId val="617378944"/>
+        <c:axId val="617380864"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="538437888"/>
+        <c:axId val="617378944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,14 +2640,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588350208"/>
+        <c:crossAx val="617380864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="588350208"/>
+        <c:axId val="617380864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,12 +2698,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="538437888"/>
+        <c:crossAx val="617378944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="588351744"/>
+        <c:axId val="617384576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2709,12 +2740,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="588359168"/>
+        <c:crossAx val="617399040"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="588359168"/>
+        <c:axId val="617399040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,7 +2754,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="588351744"/>
+        <c:crossAx val="617384576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3132,7 +3163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3209,7 +3240,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3261,13 +3292,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3279,10 +3310,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5758,6 +5789,44 @@
       </c>
       <c r="L62" s="16">
         <v>955763.61710075277</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="14">
+        <v>46142</v>
+      </c>
+      <c r="B63" s="15">
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="C63" s="15">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D63" s="16">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E63" s="16">
+        <v>-271948.26049911132</v>
+      </c>
+      <c r="F63" s="17">
+        <v>-49036.723833077041</v>
+      </c>
+      <c r="G63" s="17">
+        <v>2572201.6495263916</v>
+      </c>
+      <c r="H63" s="17">
+        <v>14264936.756843552</v>
+      </c>
+      <c r="I63" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J63" s="17">
+        <v>15492648.634443415</v>
+      </c>
+      <c r="K63" s="17">
+        <v>6116256.4467232954</v>
+      </c>
+      <c r="L63" s="16">
+        <v>1227711.877599864</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel4cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -636,6 +636,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -645,7 +648,7 @@
               <c:f>'模型四 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -827,6 +830,9 @@
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>9376392.18772012</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>9376392.18772012</c:v>
                 </c:pt>
               </c:numCache>
@@ -870,7 +876,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1053,6 +1059,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1062,7 +1071,7 @@
               <c:f>'模型四 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1245,6 +1254,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>15492648.634443415</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>16585564.304557247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1287,7 +1299,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1470,6 +1482,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1479,7 +1494,7 @@
               <c:f>'模型四 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1662,6 +1677,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>6116256.4467232954</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7209172.1168371271</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1683,11 +1701,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530836480"/>
-        <c:axId val="573232640"/>
+        <c:axId val="445511168"/>
+        <c:axId val="445513088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530836480"/>
+        <c:axId val="445511168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,14 +1748,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="573232640"/>
+        <c:crossAx val="445513088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="573232640"/>
+        <c:axId val="445513088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1788,7 +1806,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530836480"/>
+        <c:crossAx val="445511168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1979,7 +1997,7 @@
               <c:f>'模型四 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2162,6 +2180,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-271948.26049911132</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-329147.77001413936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2176,8 +2197,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="617399040"/>
-        <c:axId val="617384576"/>
+        <c:axId val="576494208"/>
+        <c:axId val="576285696"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2202,7 +2223,7 @@
               <c:f>'模型四 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2385,6 +2406,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2394,7 +2418,7 @@
               <c:f>'模型四 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2577,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>5.5458081054687502</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.970703125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2593,11 +2620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="617378944"/>
-        <c:axId val="617380864"/>
+        <c:axId val="498730880"/>
+        <c:axId val="498759552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="617378944"/>
+        <c:axId val="498730880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2640,14 +2667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617380864"/>
+        <c:crossAx val="498759552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="617380864"/>
+        <c:axId val="498759552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2698,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617378944"/>
+        <c:crossAx val="498730880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="617384576"/>
+        <c:axId val="576285696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2740,12 +2767,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="617399040"/>
+        <c:crossAx val="576494208"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="617399040"/>
+        <c:axId val="576494208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2754,7 +2781,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="617384576"/>
+        <c:crossAx val="576285696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3163,7 +3190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5829,6 +5856,44 @@
         <v>1227711.877599864</v>
       </c>
     </row>
+    <row r="64" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="14">
+        <v>46171</v>
+      </c>
+      <c r="B64" s="15">
+        <v>5.970703125</v>
+      </c>
+      <c r="C64" s="15">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D64" s="16">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E64" s="16">
+        <v>-329147.77001413936</v>
+      </c>
+      <c r="F64" s="17">
+        <v>-55127.13714335602</v>
+      </c>
+      <c r="G64" s="17">
+        <v>2517074.5123830358</v>
+      </c>
+      <c r="H64" s="17">
+        <v>15028704.656943243</v>
+      </c>
+      <c r="I64" s="17">
+        <v>9376392.18772012</v>
+      </c>
+      <c r="J64" s="17">
+        <v>16585564.304557247</v>
+      </c>
+      <c r="K64" s="17">
+        <v>7209172.1168371271</v>
+      </c>
+      <c r="L64" s="16">
+        <v>1556859.6476140034</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">
